--- a/结果/Q3_结果.xlsx
+++ b/结果/Q3_结果.xlsx
@@ -518,28 +518,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64.3</v>
+        <v>59.04</v>
       </c>
       <c r="E2" t="n">
-        <v>109.279108</v>
+        <v>109.278483</v>
       </c>
       <c r="F2" t="n">
-        <v>23.01896</v>
+        <v>23.02146</v>
       </c>
       <c r="G2" t="n">
-        <v>696.8</v>
+        <v>663.2</v>
       </c>
       <c r="H2" t="n">
-        <v>754.8</v>
+        <v>741.79</v>
       </c>
       <c r="I2" t="n">
-        <v>3104.3</v>
+        <v>3452.09</v>
       </c>
       <c r="J2" t="n">
-        <v>3632.2</v>
+        <v>3969.47</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9938</v>
+        <v>1.1014</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>300</v>
       </c>
       <c r="N2" t="n">
-        <v>68.94</v>
+        <v>65.58</v>
       </c>
       <c r="O2" t="n">
-        <v>4535.9</v>
+        <v>4916.9</v>
       </c>
     </row>
     <row r="3">
@@ -573,42 +573,42 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2419.7</v>
+        <v>2128.58</v>
       </c>
       <c r="E3" t="n">
-        <v>109.201358</v>
+        <v>109.201483</v>
       </c>
       <c r="F3" t="n">
-        <v>23.03296</v>
+        <v>23.032835</v>
       </c>
       <c r="G3" t="n">
-        <v>675.4</v>
+        <v>672.5</v>
       </c>
       <c r="H3" t="n">
-        <v>3037.5</v>
+        <v>2744.37</v>
       </c>
       <c r="I3" t="n">
-        <v>6676.9</v>
+        <v>5999.19</v>
       </c>
       <c r="J3" t="n">
-        <v>7130.3</v>
+        <v>6450.38</v>
       </c>
       <c r="K3" t="n">
-        <v>1.343</v>
+        <v>1.2244</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>58.03</v>
+        <v>61.74</v>
       </c>
       <c r="O3" t="n">
-        <v>8175.9</v>
+        <v>7447.8</v>
       </c>
     </row>
     <row r="4">
@@ -624,46 +624,46 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>M03</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5261.8</v>
+        <v>4759.15</v>
       </c>
       <c r="E4" t="n">
-        <v>109.228858</v>
+        <v>109.247608</v>
       </c>
       <c r="F4" t="n">
-        <v>23.06271</v>
+        <v>23.056585</v>
       </c>
       <c r="G4" t="n">
-        <v>528.3</v>
+        <v>586.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5974</v>
+        <v>5458.13</v>
       </c>
       <c r="I4" t="n">
-        <v>6601.2</v>
+        <v>6032.73</v>
       </c>
       <c r="J4" t="n">
-        <v>7136.8</v>
+        <v>6559.95</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4933</v>
+        <v>0.4647</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>300</v>
       </c>
       <c r="N4" t="n">
-        <v>84.58</v>
+        <v>85.48</v>
       </c>
       <c r="O4" t="n">
-        <v>7837.2</v>
+        <v>7248.7</v>
       </c>
     </row>
   </sheetData>
@@ -677,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F214"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,14 +720,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>O01→S002 爬升</t>
+          <t>O01→S013 爬升</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>450.4</v>
+        <v>450.49</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -744,14 +744,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O01→S002 巡航</t>
+          <t>O01→S013 巡航</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>450.4</v>
+        <v>450.49</v>
       </c>
       <c r="D3" t="n">
-        <v>780.4</v>
+        <v>778.0599999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -768,14 +768,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>O01→S002 巡航</t>
+          <t>O01→S013 巡航</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>780.4</v>
+        <v>778.0599999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1070</v>
+        <v>854.58</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -796,14 +796,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O01→S002 下降</t>
+          <t>O01→S013 下降</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1070</v>
+        <v>854.58</v>
       </c>
       <c r="D5" t="n">
-        <v>1105.8</v>
+        <v>873.5700000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -824,14 +824,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S002 投送</t>
+          <t>S013 投送</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1105.8</v>
+        <v>873.5700000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>1315.8</v>
+        <v>1083.57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -852,14 +852,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S002→S013 爬升</t>
+          <t>S013→O01 爬升</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1315.8</v>
+        <v>1083.57</v>
       </c>
       <c r="D7" t="n">
-        <v>1368.4</v>
+        <v>1099.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -880,14 +880,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S002→S013 巡航</t>
+          <t>S013→O01 巡航</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1368.4</v>
+        <v>1099.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1748.1</v>
+        <v>1503.48</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -908,14 +908,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S002→S013 下降</t>
+          <t>S013→O01 下降</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1748.1</v>
+        <v>1503.48</v>
       </c>
       <c r="D9" t="n">
-        <v>1758.3</v>
+        <v>1587.29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -936,129 +936,125 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S013 投送</t>
+          <t>S013→O01 下降</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1758.3</v>
+        <v>1587.29</v>
       </c>
       <c r="D10" t="n">
-        <v>1938.3</v>
+        <v>1612.07</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S013→O01 爬升</t>
+          <t>O01→S009 爬升</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1938.3</v>
+        <v>390</v>
       </c>
       <c r="D11" t="n">
-        <v>1954.1</v>
+        <v>445.18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S013→O01 巡航</t>
+          <t>O01→S009 巡航</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1954.1</v>
+        <v>445.18</v>
       </c>
       <c r="D12" t="n">
-        <v>2030.1</v>
+        <v>773.17</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S013→O01 巡航</t>
+          <t>O01→S009 巡航</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2030.1</v>
+        <v>773.17</v>
       </c>
       <c r="D13" t="n">
-        <v>2358.2</v>
+        <v>922.08</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S013→O01 下降</t>
+          <t>O01→S009 下降</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2358.2</v>
+        <v>922.08</v>
       </c>
       <c r="D14" t="n">
-        <v>2466.8</v>
+        <v>947.37</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1068,21 +1064,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>S009 投送</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>390</v>
+        <v>947.37</v>
       </c>
       <c r="D15" t="n">
-        <v>438.5</v>
+        <v>1127.37</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1092,21 +1092,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>S009→S002 爬升</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>438.5</v>
+        <v>1127.37</v>
       </c>
       <c r="D16" t="n">
-        <v>693.7</v>
+        <v>1160.13</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1116,21 +1120,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>S009→S002 巡航</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>693.7</v>
+        <v>1160.13</v>
       </c>
       <c r="D17" t="n">
-        <v>729.4</v>
+        <v>1304.38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1140,21 +1148,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>S009→S002 下降</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>729.4</v>
+        <v>1304.38</v>
       </c>
       <c r="D18" t="n">
-        <v>969.4</v>
+        <v>1347.89</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1164,21 +1176,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S001→O01 爬升</t>
+          <t>S002 投送</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>969.4</v>
+        <v>1347.89</v>
       </c>
       <c r="D19" t="n">
-        <v>999</v>
+        <v>1527.89</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1188,21 +1204,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S001→O01 巡航</t>
+          <t>S002→S013 爬升</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>999</v>
+        <v>1527.89</v>
       </c>
       <c r="D20" t="n">
-        <v>1254.3</v>
+        <v>1580.46</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1212,86 +1232,98 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S001→O01 下降</t>
+          <t>S002→S013 巡航</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1254.3</v>
+        <v>1580.46</v>
       </c>
       <c r="D21" t="n">
-        <v>1312.5</v>
+        <v>1960.17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>O01→S013 爬升</t>
+          <t>S002→S013 下降</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>360</v>
+        <v>1960.17</v>
       </c>
       <c r="D22" t="n">
-        <v>450.5</v>
+        <v>1970.38</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>O01→S013 巡航</t>
+          <t>S013 投送</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>450.5</v>
+        <v>1970.38</v>
       </c>
       <c r="D23" t="n">
-        <v>780.5</v>
+        <v>2150.38</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>O01→S013 巡航</t>
+          <t>S013→O01 爬升</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>780.5</v>
+        <v>2150.38</v>
       </c>
       <c r="D24" t="n">
-        <v>854.6</v>
+        <v>2166.21</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1307,19 +1339,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>O01→S013 下降</t>
+          <t>S013→O01 巡航</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>854.6</v>
+        <v>2166.21</v>
       </c>
       <c r="D25" t="n">
-        <v>873.6</v>
+        <v>2570.29</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1335,19 +1367,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S013 投送</t>
+          <t>S013→O01 下降</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>873.6</v>
+        <v>2570.29</v>
       </c>
       <c r="D26" t="n">
-        <v>1083.6</v>
+        <v>2654.09</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1363,30 +1395,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S013→O01 爬升</t>
+          <t>S013→O01 下降</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1083.6</v>
+        <v>2654.09</v>
       </c>
       <c r="D27" t="n">
-        <v>1099.4</v>
+        <v>2678.88</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1396,25 +1424,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S013→O01 巡航</t>
+          <t>O01→S006 爬升</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1099.4</v>
+        <v>360</v>
       </c>
       <c r="D28" t="n">
-        <v>1175.4</v>
+        <v>439.47</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1424,14 +1448,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S013→O01 巡航</t>
+          <t>O01→S006 巡航</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1175.4</v>
+        <v>439.47</v>
       </c>
       <c r="D29" t="n">
-        <v>1503.5</v>
+        <v>704.55</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1448,14 +1472,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S013→O01 下降</t>
+          <t>O01→S006 下降</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1503.5</v>
+        <v>704.55</v>
       </c>
       <c r="D30" t="n">
-        <v>1612.1</v>
+        <v>725.0700000000001</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1467,19 +1491,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>O01→S006 爬升</t>
+          <t>S006 投送</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>360</v>
+        <v>725.0700000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>439.5</v>
+        <v>935.0700000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1491,19 +1515,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>O01→S006 巡航</t>
+          <t>S006→O01 爬升</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>439.5</v>
+        <v>935.0700000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>704.6</v>
+        <v>952.17</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1515,19 +1539,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>O01→S006 下降</t>
+          <t>S006→O01 巡航</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>704.6</v>
+        <v>952.17</v>
       </c>
       <c r="D33" t="n">
-        <v>725.1</v>
+        <v>1217.25</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1539,19 +1563,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S006 投送</t>
+          <t>S006→O01 下降</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>725.1</v>
+        <v>1217.25</v>
       </c>
       <c r="D34" t="n">
-        <v>935.1</v>
+        <v>1312.61</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1568,14 +1592,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S006→O01 爬升</t>
+          <t>O01→S009 爬升</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>935.1</v>
+        <v>360</v>
       </c>
       <c r="D35" t="n">
-        <v>952.2</v>
+        <v>415.18</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1592,14 +1616,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S006→O01 巡航</t>
+          <t>O01→S009 巡航</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>952.2</v>
+        <v>415.18</v>
       </c>
       <c r="D36" t="n">
-        <v>1217.3</v>
+        <v>743.22</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1616,86 +1640,98 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S006→O01 下降</t>
+          <t>O01→S009 巡航</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1217.3</v>
+        <v>743.22</v>
       </c>
       <c r="D37" t="n">
-        <v>1312.6</v>
+        <v>892.08</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>O01→S014 爬升</t>
+          <t>O01→S009 下降</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>390</v>
+        <v>892.08</v>
       </c>
       <c r="D38" t="n">
-        <v>544.7</v>
+        <v>917.37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>O01→S014 巡航</t>
+          <t>S009 投送</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>544.7</v>
+        <v>917.37</v>
       </c>
       <c r="D39" t="n">
-        <v>807.7</v>
+        <v>1127.37</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>O01→S014 巡航</t>
+          <t>S009→O01 爬升</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>807.7</v>
+        <v>1127.37</v>
       </c>
       <c r="D40" t="n">
-        <v>905.5</v>
+        <v>1148.45</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1711,19 +1747,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>O01→S014 下降</t>
+          <t>S009→O01 巡航</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>905.5</v>
+        <v>1148.45</v>
       </c>
       <c r="D41" t="n">
-        <v>1001.9</v>
+        <v>1625.35</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1739,19 +1775,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S014 投送</t>
+          <t>S009→O01 下降</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1001.9</v>
+        <v>1625.35</v>
       </c>
       <c r="D42" t="n">
-        <v>1241.9</v>
+        <v>1666.78</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1767,30 +1803,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S014→O01 爬升</t>
+          <t>S009→O01 下降</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1241.9</v>
+        <v>1666.78</v>
       </c>
       <c r="D43" t="n">
-        <v>1322.2</v>
+        <v>1691.56</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1800,25 +1832,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S014→O01 巡航</t>
+          <t>O01→S012 爬升</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1322.2</v>
+        <v>390</v>
       </c>
       <c r="D44" t="n">
-        <v>1421.2</v>
+        <v>485.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1828,14 +1856,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>S014→O01 巡航</t>
+          <t>O01→S012 巡航</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1421.2</v>
+        <v>485.2</v>
       </c>
       <c r="D45" t="n">
-        <v>1682.9</v>
+        <v>746.88</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1852,86 +1880,98 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S014→O01 下降</t>
+          <t>O01→S012 巡航</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1682.9</v>
+        <v>746.88</v>
       </c>
       <c r="D46" t="n">
-        <v>1868.6</v>
+        <v>978.47</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>O01→S010 爬升</t>
+          <t>O01→S012 下降</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>390</v>
+        <v>978.47</v>
       </c>
       <c r="D47" t="n">
-        <v>492.6</v>
+        <v>1031.87</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>O01→S010 巡航</t>
+          <t>S012 投送</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>492.6</v>
+        <v>1031.87</v>
       </c>
       <c r="D48" t="n">
-        <v>756.6</v>
+        <v>1271.87</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>O01→S010 巡航</t>
+          <t>S012→O01 爬升</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>756.6</v>
+        <v>1271.87</v>
       </c>
       <c r="D49" t="n">
-        <v>811.2</v>
+        <v>1316.37</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1947,19 +1987,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>O01→S010 下降</t>
+          <t>S012→O01 巡航</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>811.2</v>
+        <v>1316.37</v>
       </c>
       <c r="D50" t="n">
-        <v>844.8</v>
+        <v>1809.65</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1975,19 +2015,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S010 投送</t>
+          <t>S012→O01 下降</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>844.8</v>
+        <v>1809.65</v>
       </c>
       <c r="D51" t="n">
-        <v>1084.8</v>
+        <v>1899.09</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2003,30 +2043,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S010→O01 爬升</t>
+          <t>S012→O01 下降</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1084.8</v>
+        <v>1899.09</v>
       </c>
       <c r="D52" t="n">
-        <v>1112.8</v>
+        <v>1923.89</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2036,25 +2072,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S010→O01 巡航</t>
+          <t>O01→S011 爬升</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1112.8</v>
+        <v>360</v>
       </c>
       <c r="D53" t="n">
-        <v>1168.8</v>
+        <v>415.22</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2064,14 +2096,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>S010→O01 巡航</t>
+          <t>O01→S011 巡航</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1168.8</v>
+        <v>415.22</v>
       </c>
       <c r="D54" t="n">
-        <v>1431.4</v>
+        <v>603.03</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2088,14 +2120,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S010→O01 下降</t>
+          <t>O01→S011 下降</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1431.4</v>
+        <v>603.03</v>
       </c>
       <c r="D55" t="n">
-        <v>1554.6</v>
+        <v>635.53</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2107,19 +2139,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>O01→S006 爬升</t>
+          <t>S011 投送</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>510</v>
+        <v>635.53</v>
       </c>
       <c r="D56" t="n">
-        <v>605.4</v>
+        <v>845.53</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2131,19 +2163,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>O01→S006 巡航</t>
+          <t>S011→O01 爬升</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>605.4</v>
+        <v>845.53</v>
       </c>
       <c r="D57" t="n">
-        <v>817.4</v>
+        <v>872.61</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2155,19 +2187,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>O01→S006 下降</t>
+          <t>S011→O01 巡航</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>817.4</v>
+        <v>872.61</v>
       </c>
       <c r="D58" t="n">
-        <v>843.1</v>
+        <v>1060.42</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2179,19 +2211,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S006 投送</t>
+          <t>S011→O01 下降</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>843.1</v>
+        <v>1060.42</v>
       </c>
       <c r="D59" t="n">
-        <v>1167.1</v>
+        <v>1126.68</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2208,14 +2240,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>S006→S001 爬升</t>
+          <t>O01→S001 爬升</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1167.1</v>
+        <v>510</v>
       </c>
       <c r="D60" t="n">
-        <v>1198.7</v>
+        <v>568.14</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2232,14 +2264,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S006→S001 巡航</t>
+          <t>O01→S001 巡航</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1198.7</v>
+        <v>568.14</v>
       </c>
       <c r="D61" t="n">
-        <v>1551.8</v>
+        <v>772.37</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2256,14 +2288,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S006→S001 下降</t>
+          <t>O01→S001 下降</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1551.8</v>
+        <v>772.37</v>
       </c>
       <c r="D62" t="n">
-        <v>1656.8</v>
+        <v>816.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2284,10 +2316,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1656.8</v>
+        <v>816.9</v>
       </c>
       <c r="D63" t="n">
-        <v>1944.8</v>
+        <v>1248.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2308,10 +2340,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1944.8</v>
+        <v>1248.9</v>
       </c>
       <c r="D64" t="n">
-        <v>1980.4</v>
+        <v>1284.52</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2332,10 +2364,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1980.4</v>
+        <v>1284.52</v>
       </c>
       <c r="D65" t="n">
-        <v>2184.7</v>
+        <v>1488.75</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2356,10 +2388,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2184.7</v>
+        <v>1488.75</v>
       </c>
       <c r="D66" t="n">
-        <v>2257.3</v>
+        <v>1561.43</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2376,14 +2408,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>O01→S002 爬升</t>
+          <t>O01→S001 爬升</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="D67" t="n">
-        <v>552.5</v>
+        <v>598.14</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2400,14 +2432,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>O01→S002 巡航</t>
+          <t>O01→S001 巡航</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>552.5</v>
+        <v>598.14</v>
       </c>
       <c r="D68" t="n">
-        <v>816.5</v>
+        <v>802.37</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2424,25 +2456,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>O01→S002 巡航</t>
+          <t>O01→S001 下降</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>816.5</v>
+        <v>802.37</v>
       </c>
       <c r="D69" t="n">
-        <v>1048.2</v>
+        <v>846.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2452,25 +2480,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>O01→S002 下降</t>
+          <t>S001 投送</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1048.2</v>
+        <v>846.9</v>
       </c>
       <c r="D70" t="n">
-        <v>1092.9</v>
+        <v>1314.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2480,25 +2504,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S002 投送</t>
+          <t>S001→O01 爬升</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1092.9</v>
+        <v>1314.9</v>
       </c>
       <c r="D71" t="n">
-        <v>1488.9</v>
+        <v>1350.52</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2508,25 +2528,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S002→O01 爬升</t>
+          <t>S001→O01 巡航</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1488.9</v>
+        <v>1350.52</v>
       </c>
       <c r="D72" t="n">
-        <v>1524.7</v>
+        <v>1554.75</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2536,42 +2552,38 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S002→O01 巡航</t>
+          <t>S001→O01 下降</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1524.7</v>
+        <v>1554.75</v>
       </c>
       <c r="D73" t="n">
-        <v>1757.7</v>
+        <v>1627.43</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S002→O01 巡航</t>
+          <t>O01→S010 爬升</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1757.7</v>
+        <v>1516.7</v>
       </c>
       <c r="D74" t="n">
-        <v>2020.4</v>
+        <v>1619.35</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2583,19 +2595,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>S002→O01 下降</t>
+          <t>O01→S010 巡航</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2020.4</v>
+        <v>1619.35</v>
       </c>
       <c r="D75" t="n">
-        <v>2111</v>
+        <v>1880.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2612,21 +2624,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>O01→S010 巡航</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1672.5</v>
+        <v>1880.9</v>
       </c>
       <c r="D76" t="n">
-        <v>1720.9</v>
+        <v>1937.92</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2636,21 +2652,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>O01→S010 下降</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1720.9</v>
+        <v>1937.92</v>
       </c>
       <c r="D77" t="n">
-        <v>1976.2</v>
+        <v>1971.53</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2660,21 +2680,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>S010 投送</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1976.2</v>
+        <v>1971.53</v>
       </c>
       <c r="D78" t="n">
-        <v>2011.8</v>
+        <v>2211.53</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2684,21 +2708,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>S010→O01 爬升</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2011.8</v>
+        <v>2211.53</v>
       </c>
       <c r="D79" t="n">
-        <v>2221.8</v>
+        <v>2239.55</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2708,21 +2736,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S001→O01 爬升</t>
+          <t>S010→O01 巡航</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2221.8</v>
+        <v>2239.55</v>
       </c>
       <c r="D80" t="n">
-        <v>2251.5</v>
+        <v>2558.12</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2732,21 +2764,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>S001→O01 巡航</t>
+          <t>S010→O01 下降</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2251.5</v>
+        <v>2558.12</v>
       </c>
       <c r="D81" t="n">
-        <v>2506.8</v>
+        <v>2656.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2756,14 +2792,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>S001→O01 下降</t>
+          <t>S010→O01 下降</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2506.8</v>
+        <v>2656.5</v>
       </c>
       <c r="D82" t="n">
-        <v>2565</v>
+        <v>2681.3</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2780,14 +2816,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>O01→S006 爬升</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1672.6</v>
+        <v>1672.7</v>
       </c>
       <c r="D83" t="n">
-        <v>1721.1</v>
+        <v>1752.17</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2804,14 +2840,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>O01→S006 巡航</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1721.1</v>
+        <v>1752.17</v>
       </c>
       <c r="D84" t="n">
-        <v>1976.4</v>
+        <v>2017.25</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2828,14 +2864,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>O01→S006 下降</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1976.4</v>
+        <v>2017.25</v>
       </c>
       <c r="D85" t="n">
-        <v>2012</v>
+        <v>2037.77</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2852,14 +2888,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>S006 投送</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2012</v>
+        <v>2037.77</v>
       </c>
       <c r="D86" t="n">
-        <v>2222</v>
+        <v>2247.77</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2876,14 +2912,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>S001→O01 爬升</t>
+          <t>S006→O01 爬升</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2222</v>
+        <v>2247.77</v>
       </c>
       <c r="D87" t="n">
-        <v>2251.7</v>
+        <v>2264.87</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2900,14 +2936,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>S001→O01 巡航</t>
+          <t>S006→O01 巡航</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2251.7</v>
+        <v>2264.87</v>
       </c>
       <c r="D88" t="n">
-        <v>2506.9</v>
+        <v>2529.95</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2924,14 +2960,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>S001→O01 下降</t>
+          <t>S006→O01 下降</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2506.9</v>
+        <v>2529.95</v>
       </c>
       <c r="D89" t="n">
-        <v>2565.1</v>
+        <v>2625.31</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2948,14 +2984,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>O01→S012 爬升</t>
+          <t>O01→S006 爬升</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1944.6</v>
+        <v>2071.5</v>
       </c>
       <c r="D90" t="n">
-        <v>2039.8</v>
+        <v>2166.86</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2972,14 +3008,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>O01→S012 巡航</t>
+          <t>O01→S006 巡航</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2039.8</v>
+        <v>2166.86</v>
       </c>
       <c r="D91" t="n">
-        <v>2303.8</v>
+        <v>2378.93</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2996,25 +3032,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>O01→S012 巡航</t>
+          <t>O01→S006 下降</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2303.8</v>
+        <v>2378.93</v>
       </c>
       <c r="D92" t="n">
-        <v>2533.1</v>
+        <v>2404.58</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3024,25 +3056,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>O01→S012 下降</t>
+          <t>S006 投送</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2533.1</v>
+        <v>2404.58</v>
       </c>
       <c r="D93" t="n">
-        <v>2586.5</v>
+        <v>2656.58</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3052,25 +3080,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>S012 投送</t>
+          <t>S006→S007 爬升</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2586.5</v>
+        <v>2656.58</v>
       </c>
       <c r="D94" t="n">
-        <v>2826.5</v>
+        <v>2766.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3080,25 +3104,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S012→O01 爬升</t>
+          <t>S006→S007 巡航</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2826.5</v>
+        <v>2766.8</v>
       </c>
       <c r="D95" t="n">
-        <v>2871</v>
+        <v>2881.35</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3108,14 +3128,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S012→O01 巡航</t>
+          <t>S006→S007 巡航</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2871</v>
+        <v>2881.35</v>
       </c>
       <c r="D96" t="n">
-        <v>3102</v>
+        <v>2934.57</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3124,7 +3144,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -3136,21 +3156,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S012→O01 巡航</t>
+          <t>S006→S007 下降</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3102</v>
+        <v>2934.57</v>
       </c>
       <c r="D97" t="n">
-        <v>3364.2</v>
+        <v>3055.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3160,110 +3184,126 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S012→O01 下降</t>
+          <t>S007 投送</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3364.2</v>
+        <v>3055.5</v>
       </c>
       <c r="D98" t="n">
-        <v>3478.5</v>
+        <v>3415.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>S007→O01 爬升</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2228.6</v>
+        <v>3415.5</v>
       </c>
       <c r="D99" t="n">
-        <v>2277</v>
+        <v>3480.89</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>S007→O01 巡航</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2277</v>
+        <v>3480.89</v>
       </c>
       <c r="D100" t="n">
-        <v>2481.3</v>
+        <v>3783.16</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>S007→O01 下降</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2481.3</v>
+        <v>3783.16</v>
       </c>
       <c r="D101" t="n">
-        <v>2516.9</v>
+        <v>3968.99</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>S007→O01 下降</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2516.9</v>
+        <v>3968.99</v>
       </c>
       <c r="D102" t="n">
-        <v>2726.9</v>
+        <v>3975.3</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3280,14 +3320,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S001→O01 爬升</t>
+          <t>O01→S011 爬升</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2726.9</v>
+        <v>2002.1</v>
       </c>
       <c r="D103" t="n">
-        <v>2756.6</v>
+        <v>2057.32</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3304,14 +3344,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S001→O01 巡航</t>
+          <t>O01→S011 巡航</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2756.6</v>
+        <v>2057.32</v>
       </c>
       <c r="D104" t="n">
-        <v>2960.8</v>
+        <v>2292.08</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3328,14 +3368,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>S001→O01 下降</t>
+          <t>O01→S011 下降</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2960.8</v>
+        <v>2292.08</v>
       </c>
       <c r="D105" t="n">
-        <v>3019</v>
+        <v>2324.58</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3347,19 +3387,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>O01→S007 爬升</t>
+          <t>S011 投送</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2621</v>
+        <v>2324.58</v>
       </c>
       <c r="D106" t="n">
-        <v>2774.7</v>
+        <v>2504.58</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3371,19 +3411,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>O01→S007 巡航</t>
+          <t>S011→S015 爬升</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2774.7</v>
+        <v>2504.58</v>
       </c>
       <c r="D107" t="n">
-        <v>3037.7</v>
+        <v>2629.96</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3395,47 +3435,43 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>O01→S007 巡航</t>
+          <t>S011→S015 巡航</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3037.7</v>
+        <v>2629.96</v>
       </c>
       <c r="D108" t="n">
-        <v>3077</v>
+        <v>2747.69</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>O01→S007 下降</t>
+          <t>S011→S015 巡航</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3077</v>
+        <v>2747.69</v>
       </c>
       <c r="D109" t="n">
-        <v>3158.8</v>
+        <v>2918.48</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3451,19 +3487,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>S007 投送</t>
+          <t>S011→S015 下降</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3158.8</v>
+        <v>2918.48</v>
       </c>
       <c r="D110" t="n">
-        <v>3446.8</v>
+        <v>2963.97</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3479,19 +3515,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>S007→S003 爬升</t>
+          <t>S015 投送</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3446.8</v>
+        <v>2963.97</v>
       </c>
       <c r="D111" t="n">
-        <v>3471.6</v>
+        <v>3143.97</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3507,19 +3543,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>S007→S003 巡航</t>
+          <t>S015→S003 爬升</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3471.6</v>
+        <v>3143.97</v>
       </c>
       <c r="D112" t="n">
-        <v>3653.9</v>
+        <v>3148.44</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3535,19 +3571,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>S007→S003 下降</t>
+          <t>S015→S003 巡航</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3653.9</v>
+        <v>3148.44</v>
       </c>
       <c r="D113" t="n">
-        <v>3690</v>
+        <v>3366.35</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3563,19 +3599,19 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>S003 投送</t>
+          <t>S015→S003 下降</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3690</v>
+        <v>3366.35</v>
       </c>
       <c r="D114" t="n">
-        <v>4014</v>
+        <v>3426.11</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3591,19 +3627,19 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>S003→O01 爬升</t>
+          <t>S003 投送</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4014</v>
+        <v>3426.11</v>
       </c>
       <c r="D115" t="n">
-        <v>4103.3</v>
+        <v>3606.11</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3619,19 +3655,19 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>S003→O01 巡航</t>
+          <t>S003→O01 爬升</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4103.3</v>
+        <v>3606.11</v>
       </c>
       <c r="D116" t="n">
-        <v>4325.3</v>
+        <v>3680.55</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3647,7 +3683,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3656,22 +3692,26 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4325.3</v>
+        <v>3680.55</v>
       </c>
       <c r="D117" t="n">
-        <v>4587.4</v>
+        <v>4285.69</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3680,34 +3720,38 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4587.4</v>
+        <v>4285.69</v>
       </c>
       <c r="D118" t="n">
-        <v>4804.4</v>
+        <v>4453.99</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>O01→S011 爬升</t>
+          <t>S003→O01 下降</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2538.8</v>
+        <v>4453.99</v>
       </c>
       <c r="D119" t="n">
-        <v>2594</v>
+        <v>4459.33</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3719,19 +3763,19 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>O01→S011 巡航</t>
+          <t>O01→S002 爬升</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2594</v>
+        <v>2137.5</v>
       </c>
       <c r="D120" t="n">
-        <v>2828.8</v>
+        <v>2210</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3743,19 +3787,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>O01→S011 下降</t>
+          <t>O01→S002 巡航</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2828.8</v>
+        <v>2210</v>
       </c>
       <c r="D121" t="n">
-        <v>2861.3</v>
+        <v>2472.07</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -3767,139 +3811,159 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>S011 投送</t>
+          <t>O01→S002 巡航</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2861.3</v>
+        <v>2472.07</v>
       </c>
       <c r="D122" t="n">
-        <v>3071.3</v>
+        <v>2705.7</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>S011→O01 爬升</t>
+          <t>O01→S002 下降</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3071.3</v>
+        <v>2705.7</v>
       </c>
       <c r="D123" t="n">
-        <v>3098.4</v>
+        <v>2750.43</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>S011→O01 巡航</t>
+          <t>S002 投送</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3098.4</v>
+        <v>2750.43</v>
       </c>
       <c r="D124" t="n">
-        <v>3333.1</v>
+        <v>3182.43</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>S011→O01 下降</t>
+          <t>S002→O01 爬升</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3333.1</v>
+        <v>3182.43</v>
       </c>
       <c r="D125" t="n">
-        <v>3399.4</v>
+        <v>3218.21</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>O01→S001 爬升</t>
+          <t>S002→O01 巡航</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2767.3</v>
+        <v>3218.21</v>
       </c>
       <c r="D126" t="n">
-        <v>2825.5</v>
+        <v>3451.24</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>O01→S001 巡航</t>
+          <t>S002→O01 巡航</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2825.5</v>
+        <v>3451.24</v>
       </c>
       <c r="D127" t="n">
-        <v>3029.7</v>
+        <v>3713.91</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3911,19 +3975,19 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>O01→S001 下降</t>
+          <t>S002→O01 下降</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3029.7</v>
+        <v>3713.91</v>
       </c>
       <c r="D128" t="n">
-        <v>3074.2</v>
+        <v>3804.54</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -3935,19 +3999,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>S001 投送</t>
+          <t>O01→S014 爬升</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3074.2</v>
+        <v>2313.9</v>
       </c>
       <c r="D129" t="n">
-        <v>3362.2</v>
+        <v>2468.65</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -3959,19 +4023,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>S001→S005 爬升</t>
+          <t>O01→S014 巡航</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3362.2</v>
+        <v>2468.65</v>
       </c>
       <c r="D130" t="n">
-        <v>3415.1</v>
+        <v>2729.27</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3983,43 +4047,47 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>S001→S005 巡航</t>
+          <t>O01→S014 巡航</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3415.1</v>
+        <v>2729.27</v>
       </c>
       <c r="D131" t="n">
-        <v>3503.1</v>
+        <v>2829.37</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>S001→S005 巡航</t>
+          <t>O01→S014 下降</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3503.1</v>
+        <v>2829.37</v>
       </c>
       <c r="D132" t="n">
-        <v>3610.8</v>
+        <v>2925.75</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4028,26 +4096,26 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>S001→S005 下降</t>
+          <t>S014 投送</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3610.8</v>
+        <v>2925.75</v>
       </c>
       <c r="D133" t="n">
-        <v>3671.4</v>
+        <v>3165.75</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4056,26 +4124,26 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>S005 投送</t>
+          <t>S014→O01 爬升</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3671.4</v>
+        <v>3165.75</v>
       </c>
       <c r="D134" t="n">
-        <v>3995.4</v>
+        <v>3246.07</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4084,26 +4152,26 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>S005→O01 爬升</t>
+          <t>S014→O01 巡航</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3995.4</v>
+        <v>3246.07</v>
       </c>
       <c r="D135" t="n">
-        <v>4047.9</v>
+        <v>3450.6</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4112,54 +4180,50 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>S005→O01 巡航</t>
+          <t>S014→O01 巡航</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4047.9</v>
+        <v>3450.6</v>
       </c>
       <c r="D136" t="n">
-        <v>4137.9</v>
+        <v>3606.79</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>S005→O01 巡航</t>
+          <t>S014→O01 下降</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4137.9</v>
+        <v>3606.79</v>
       </c>
       <c r="D137" t="n">
-        <v>4401.4</v>
+        <v>3792.49</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4176,14 +4240,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>S005→O01 下降</t>
+          <t>O01→S015 爬升</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4401.4</v>
+        <v>2551</v>
       </c>
       <c r="D138" t="n">
-        <v>4500.8</v>
+        <v>2699.03</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4195,19 +4259,19 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>O01→S011 爬升</t>
+          <t>O01→S015 巡航</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2856.8</v>
+        <v>2699.03</v>
       </c>
       <c r="D139" t="n">
-        <v>2912</v>
+        <v>3025.36</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4219,139 +4283,159 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>O01→S011 巡航</t>
+          <t>O01→S015 巡航</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2912</v>
+        <v>3025.36</v>
       </c>
       <c r="D140" t="n">
-        <v>3146.8</v>
+        <v>3200.66</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>O01→S011 下降</t>
+          <t>O01→S015 下降</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3146.8</v>
+        <v>3200.66</v>
       </c>
       <c r="D141" t="n">
-        <v>3179.3</v>
+        <v>3239.58</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>S011 投送</t>
+          <t>S015 投送</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3179.3</v>
+        <v>3239.58</v>
       </c>
       <c r="D142" t="n">
-        <v>3359.3</v>
+        <v>3449.58</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S011→S005 爬升</t>
+          <t>S015→O01 爬升</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3359.3</v>
+        <v>3449.58</v>
       </c>
       <c r="D143" t="n">
-        <v>3404.4</v>
+        <v>3482.01</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>S015→O01 巡航</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3404.4</v>
+        <v>3482.01</v>
       </c>
       <c r="D144" t="n">
-        <v>3517.4</v>
+        <v>3983.64</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>S015→O01 下降</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3517.4</v>
+        <v>3983.64</v>
       </c>
       <c r="D145" t="n">
-        <v>3554.4</v>
+        <v>4155.96</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4367,19 +4451,19 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>S015→O01 下降</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3554.4</v>
+        <v>4155.96</v>
       </c>
       <c r="D146" t="n">
-        <v>3559.4</v>
+        <v>4161.28</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4396,25 +4480,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>O01→S008 爬升</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3559.4</v>
+        <v>3041.3</v>
       </c>
       <c r="D147" t="n">
-        <v>3585.4</v>
+        <v>3123.04</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4424,14 +4504,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>O01→S008 巡航</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3585.4</v>
+        <v>3123.04</v>
       </c>
       <c r="D148" t="n">
-        <v>3633.4</v>
+        <v>3415.57</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4448,14 +4528,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>S011→S005 巡航</t>
+          <t>O01→S008 巡航</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3633.4</v>
+        <v>3415.57</v>
       </c>
       <c r="D149" t="n">
-        <v>3638.8</v>
+        <v>3663.67</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4476,14 +4556,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>S011→S005 下降</t>
+          <t>O01→S008 下降</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3638.8</v>
+        <v>3663.67</v>
       </c>
       <c r="D150" t="n">
-        <v>3699.9</v>
+        <v>3704.48</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4504,14 +4584,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>S005 投送</t>
+          <t>S008 投送</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3699.9</v>
+        <v>3704.48</v>
       </c>
       <c r="D151" t="n">
-        <v>3909.9</v>
+        <v>3914.48</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4532,14 +4612,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>S005→O01 爬升</t>
+          <t>S008→O01 爬升</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3909.9</v>
+        <v>3914.48</v>
       </c>
       <c r="D152" t="n">
-        <v>3953.7</v>
+        <v>3948.48</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4560,14 +4640,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>S005→O01 巡航</t>
+          <t>S008→O01 巡航</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3953.7</v>
+        <v>3948.48</v>
       </c>
       <c r="D153" t="n">
-        <v>4066.7</v>
+        <v>4489.12</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4588,21 +4668,25 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>S005→O01 巡航</t>
+          <t>S008→O01 下降</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4066.7</v>
+        <v>4489.12</v>
       </c>
       <c r="D154" t="n">
-        <v>4395.5</v>
+        <v>4581.87</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4612,14 +4696,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>S005→O01 下降</t>
+          <t>S008→O01 下降</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4395.5</v>
+        <v>4581.87</v>
       </c>
       <c r="D155" t="n">
-        <v>4475</v>
+        <v>4587.2</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -4636,14 +4720,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>O01→S008 爬升</t>
+          <t>O01→S005 爬升</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3379</v>
+        <v>3057.2</v>
       </c>
       <c r="D156" t="n">
-        <v>3460.7</v>
+        <v>3123.44</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -4660,14 +4744,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>O01→S008 巡航</t>
+          <t>O01→S005 巡航</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3460.7</v>
+        <v>3123.44</v>
       </c>
       <c r="D157" t="n">
-        <v>3754.7</v>
+        <v>3451.3</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4684,14 +4768,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>O01→S008 巡航</t>
+          <t>O01→S005 巡航</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3754.7</v>
+        <v>3451.3</v>
       </c>
       <c r="D158" t="n">
-        <v>4001.3</v>
+        <v>3565.27</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -4712,14 +4796,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>O01→S008 下降</t>
+          <t>O01→S005 下降</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4001.3</v>
+        <v>3565.27</v>
       </c>
       <c r="D159" t="n">
-        <v>4042.1</v>
+        <v>3617.84</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -4740,14 +4824,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>S008 投送</t>
+          <t>S005 投送</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4042.1</v>
+        <v>3617.84</v>
       </c>
       <c r="D160" t="n">
-        <v>4252.1</v>
+        <v>3827.84</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -4768,14 +4852,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>S008→O01 爬升</t>
+          <t>S005→O01 爬升</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4252.1</v>
+        <v>3827.84</v>
       </c>
       <c r="D161" t="n">
-        <v>4286.1</v>
+        <v>3871.64</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4796,14 +4880,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>S008→O01 巡航</t>
+          <t>S005→O01 巡航</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4286.1</v>
+        <v>3871.64</v>
       </c>
       <c r="D162" t="n">
-        <v>4533.1</v>
+        <v>4313.47</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -4824,21 +4908,25 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>S008→O01 巡航</t>
+          <t>S005→O01 下降</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4533.1</v>
+        <v>4313.47</v>
       </c>
       <c r="D163" t="n">
-        <v>4826.8</v>
+        <v>4387.65</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4848,14 +4936,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>S008→O01 下降</t>
+          <t>S005→O01 下降</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4826.8</v>
+        <v>4387.65</v>
       </c>
       <c r="D164" t="n">
-        <v>4924.9</v>
+        <v>4392.96</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -4876,10 +4964,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3868.5</v>
+        <v>4182.5</v>
       </c>
       <c r="D165" t="n">
-        <v>3950.2</v>
+        <v>4264.24</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -4900,10 +4988,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3950.2</v>
+        <v>4264.24</v>
       </c>
       <c r="D166" t="n">
-        <v>4244.2</v>
+        <v>4556.77</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -4924,10 +5012,10 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4244.2</v>
+        <v>4556.77</v>
       </c>
       <c r="D167" t="n">
-        <v>4490.9</v>
+        <v>4804.87</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -4952,10 +5040,10 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4490.9</v>
+        <v>4804.87</v>
       </c>
       <c r="D168" t="n">
-        <v>4531.7</v>
+        <v>4845.68</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -4980,10 +5068,10 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4531.7</v>
+        <v>4845.68</v>
       </c>
       <c r="D169" t="n">
-        <v>4771.7</v>
+        <v>5085.68</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5008,10 +5096,10 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4771.7</v>
+        <v>5085.68</v>
       </c>
       <c r="D170" t="n">
-        <v>4805.7</v>
+        <v>5119.68</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5036,10 +5124,10 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4805.7</v>
+        <v>5119.68</v>
       </c>
       <c r="D171" t="n">
-        <v>5052.7</v>
+        <v>5660.32</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5060,21 +5148,25 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>S008→O01 巡航</t>
+          <t>S008→O01 下降</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>5052.7</v>
+        <v>5660.32</v>
       </c>
       <c r="D172" t="n">
-        <v>5346.3</v>
+        <v>5753.07</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5088,10 +5180,10 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5346.3</v>
+        <v>5753.07</v>
       </c>
       <c r="D173" t="n">
-        <v>5444.4</v>
+        <v>5758.4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5108,14 +5200,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>O01→S007 爬升</t>
+          <t>O01→S005 爬升</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>4980.8</v>
+        <v>4344.6</v>
       </c>
       <c r="D174" t="n">
-        <v>5134.5</v>
+        <v>4424.08</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -5132,14 +5224,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>O01→S007 巡航</t>
+          <t>O01→S005 巡航</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5134.5</v>
+        <v>4424.08</v>
       </c>
       <c r="D175" t="n">
-        <v>5397.5</v>
+        <v>4686.08</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5156,14 +5248,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>O01→S007 巡航</t>
+          <t>O01→S005 巡航</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5397.5</v>
+        <v>4686.08</v>
       </c>
       <c r="D176" t="n">
-        <v>5436.7</v>
+        <v>4777.55</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -5184,14 +5276,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>O01→S007 下降</t>
+          <t>O01→S005 下降</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>5436.7</v>
+        <v>4777.55</v>
       </c>
       <c r="D177" t="n">
-        <v>5518.5</v>
+        <v>4843.26</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -5212,14 +5304,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>S007 投送</t>
+          <t>S005 投送</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5518.5</v>
+        <v>4843.26</v>
       </c>
       <c r="D178" t="n">
-        <v>5770.5</v>
+        <v>5167.26</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5240,14 +5332,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>S007→S003 爬升</t>
+          <t>S005→S004 爬升</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5770.5</v>
+        <v>5167.26</v>
       </c>
       <c r="D179" t="n">
-        <v>5795.4</v>
+        <v>5235.58</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5268,14 +5360,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>S007→S003 巡航</t>
+          <t>S005→S004 巡航</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5795.4</v>
+        <v>5235.58</v>
       </c>
       <c r="D180" t="n">
-        <v>5977.6</v>
+        <v>5410.03</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5296,14 +5388,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S007→S003 下降</t>
+          <t>S005→S004 下降</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5977.6</v>
+        <v>5410.03</v>
       </c>
       <c r="D181" t="n">
-        <v>6013.7</v>
+        <v>5460.17</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5324,14 +5416,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S003 投送</t>
+          <t>S005→S004 下降</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>6013.7</v>
+        <v>5460.17</v>
       </c>
       <c r="D182" t="n">
-        <v>6337.7</v>
+        <v>5478.78</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -5340,7 +5432,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -5352,14 +5444,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S003→O01 爬升</t>
+          <t>S004 投送</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>6337.7</v>
+        <v>5478.78</v>
       </c>
       <c r="D183" t="n">
-        <v>6427</v>
+        <v>5802.78</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5368,7 +5460,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -5380,14 +5472,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S003→O01 巡航</t>
+          <t>S004→O01 爬升</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>6427</v>
+        <v>5802.78</v>
       </c>
       <c r="D184" t="n">
-        <v>6649</v>
+        <v>5870.75</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -5396,7 +5488,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -5408,21 +5500,25 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S003→O01 巡航</t>
+          <t>S004→O01 巡航</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>6649</v>
+        <v>5870.75</v>
       </c>
       <c r="D185" t="n">
-        <v>6911.1</v>
+        <v>6031.27</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5432,14 +5528,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S003→O01 下降</t>
+          <t>S004→O01 巡航</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>6911.1</v>
+        <v>6031.27</v>
       </c>
       <c r="D186" t="n">
-        <v>7128.2</v>
+        <v>6387.13</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -5451,19 +5547,19 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>O01→S004 爬升</t>
+          <t>S004→O01 下降</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>5284.4</v>
+        <v>6387.13</v>
       </c>
       <c r="D187" t="n">
-        <v>5392.7</v>
+        <v>6522.4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -5480,14 +5576,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>O01→S004 巡航</t>
+          <t>O01→S003 爬升</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>5392.7</v>
+        <v>4485.3</v>
       </c>
       <c r="D188" t="n">
-        <v>5767.7</v>
+        <v>4658.94</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -5504,25 +5600,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>O01→S004 巡航</t>
+          <t>O01→S003 巡航</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>5767.7</v>
+        <v>4658.94</v>
       </c>
       <c r="D189" t="n">
-        <v>5909</v>
+        <v>4919.77</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连G01</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5532,14 +5624,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>O01→S004 下降</t>
+          <t>O01→S003 巡航</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>5909</v>
+        <v>4919.77</v>
       </c>
       <c r="D190" t="n">
-        <v>5977</v>
+        <v>5143.06</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -5560,14 +5652,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>O01→S004 下降</t>
+          <t>O01→S003 下降</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>5977</v>
+        <v>5143.06</v>
       </c>
       <c r="D191" t="n">
-        <v>5994</v>
+        <v>5254.71</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -5576,7 +5668,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -5588,14 +5680,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>S004 投送</t>
+          <t>S003 投送</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>5994</v>
+        <v>5254.71</v>
       </c>
       <c r="D192" t="n">
-        <v>6390</v>
+        <v>5686.71</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -5604,7 +5696,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -5616,14 +5708,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>S004→O01 爬升</t>
+          <t>S003→O01 爬升</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>6390</v>
+        <v>5686.71</v>
       </c>
       <c r="D193" t="n">
-        <v>6458</v>
+        <v>5776.03</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -5632,7 +5724,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -5644,14 +5736,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>S004→O01 巡航</t>
+          <t>S003→O01 巡航</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>6458</v>
+        <v>5776.03</v>
       </c>
       <c r="D194" t="n">
-        <v>6600</v>
+        <v>5998.52</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -5660,7 +5752,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -5672,14 +5764,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>S004→O01 巡航</t>
+          <t>S003→O01 巡航</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>6600</v>
+        <v>5998.52</v>
       </c>
       <c r="D195" t="n">
-        <v>6974.4</v>
+        <v>6260.14</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -5696,14 +5788,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>S004→O01 下降</t>
+          <t>S003→O01 下降</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>6974.4</v>
+        <v>6260.14</v>
       </c>
       <c r="D196" t="n">
-        <v>7109.6</v>
+        <v>6477.2</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -5720,14 +5812,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>O01→S015 爬升</t>
+          <t>O01→S004 爬升</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>5314.9</v>
+        <v>4947.3</v>
       </c>
       <c r="D197" t="n">
-        <v>5462.9</v>
+        <v>5037.48</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -5744,14 +5836,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>O01→S015 巡航</t>
+          <t>O01→S004 巡航</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>5462.9</v>
+        <v>5037.48</v>
       </c>
       <c r="D198" t="n">
-        <v>5725.9</v>
+        <v>5410.99</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -5768,14 +5860,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>O01→S015 巡航</t>
+          <t>O01→S004 巡航</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>5725.9</v>
+        <v>5410.99</v>
       </c>
       <c r="D199" t="n">
-        <v>5864.2</v>
+        <v>5553.86</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -5796,14 +5888,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>O01→S015 下降</t>
+          <t>O01→S004 下降</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>5864.2</v>
+        <v>5553.86</v>
       </c>
       <c r="D200" t="n">
-        <v>5903.1</v>
+        <v>5606.66</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5824,14 +5916,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>S015 投送</t>
+          <t>O01→S004 下降</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>5903.1</v>
+        <v>5606.66</v>
       </c>
       <c r="D201" t="n">
-        <v>6143.1</v>
+        <v>5621.83</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5840,7 +5932,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -5852,14 +5944,14 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>S015→O01 爬升</t>
+          <t>S004 投送</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>6143.1</v>
+        <v>5621.83</v>
       </c>
       <c r="D202" t="n">
-        <v>6175.5</v>
+        <v>5831.83</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -5868,7 +5960,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -5880,14 +5972,14 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>S015→O01 巡航</t>
+          <t>S004→O01 爬升</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>6175.5</v>
+        <v>5831.83</v>
       </c>
       <c r="D203" t="n">
-        <v>6315.5</v>
+        <v>5888.48</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -5896,7 +5988,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
@@ -5908,21 +6000,25 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>S015→O01 巡航</t>
+          <t>S004→O01 巡航</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>6315.5</v>
+        <v>5888.48</v>
       </c>
       <c r="D204" t="n">
-        <v>6576.8</v>
+        <v>6031.3</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5932,14 +6028,14 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>S015→O01 下降</t>
+          <t>S004→O01 巡航</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>6576.8</v>
+        <v>6031.3</v>
       </c>
       <c r="D205" t="n">
-        <v>6754.5</v>
+        <v>6404.86</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5951,19 +6047,19 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Q3-T22</t>
+          <t>Q3-T21</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>O01→S009 爬升</t>
+          <t>S004→O01 下降</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>5834.4</v>
+        <v>6404.86</v>
       </c>
       <c r="D206" t="n">
-        <v>5889.6</v>
+        <v>6513.07</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -5971,218 +6067,6 @@
         </is>
       </c>
       <c r="F206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>O01→S009 巡航</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>5889.6</v>
-      </c>
-      <c r="D207" t="n">
-        <v>6153.6</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>O01→S009 巡航</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>6153.6</v>
-      </c>
-      <c r="D208" t="n">
-        <v>6271.1</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>O01→S009 下降</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>6271.1</v>
-      </c>
-      <c r="D209" t="n">
-        <v>6296.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>S009 投送</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>6296.4</v>
-      </c>
-      <c r="D210" t="n">
-        <v>6536.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>S009→O01 爬升</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>6536.4</v>
-      </c>
-      <c r="D211" t="n">
-        <v>6557.5</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>S009→O01 巡航</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>6557.5</v>
-      </c>
-      <c r="D212" t="n">
-        <v>6675.5</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>S009→O01 巡航</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>6675.5</v>
-      </c>
-      <c r="D213" t="n">
-        <v>6939</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>S009→O01 下降</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>6939</v>
-      </c>
-      <c r="D214" t="n">
-        <v>7005.2</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>直连G01</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6195,7 +6079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6301,32 +6185,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>O01→S002→S013→O01</t>
+          <t>O01→S013→O01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2466.8</v>
+        <v>1612.1</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3797</v>
+        <v>2.0253</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="K2" t="n">
-        <v>24.9</v>
+        <v>54.99</v>
       </c>
       <c r="L2" t="n">
-        <v>3943.2</v>
+        <v>2697.2</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1249.7</v>
+        <v>809.2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -6360,14 +6244,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S009→S002→S013→O01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1312.5</v>
+        <v>2678.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.268</v>
+        <v>3.3978</v>
       </c>
       <c r="I3" t="n">
         <v>20</v>
@@ -6376,20 +6260,20 @@
         <v>0.051</v>
       </c>
       <c r="K3" t="n">
-        <v>71.81999999999999</v>
+        <v>24.49</v>
       </c>
       <c r="L3" t="n">
-        <v>2178.8</v>
+        <v>4160.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1880.9</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>无（全程直连）</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
@@ -6419,36 +6303,36 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O01→S013→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1612.1</v>
+        <v>1312.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0253</v>
+        <v>1.3096</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>0.055</v>
+        <v>0.039</v>
       </c>
       <c r="K4" t="n">
-        <v>54.99</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>2697.2</v>
+        <v>2190.9</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>394.9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>无（全程直连）</t>
         </is>
       </c>
     </row>
@@ -6478,14 +6362,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>O01→S006→O01</t>
+          <t>O01→S009→O01</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1312.6</v>
+        <v>1691.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.355</v>
+        <v>2.3383</v>
       </c>
       <c r="I5" t="n">
         <v>22</v>
@@ -6494,20 +6378,20 @@
         <v>0.055</v>
       </c>
       <c r="K5" t="n">
-        <v>69.89</v>
+        <v>48.04</v>
       </c>
       <c r="L5" t="n">
-        <v>2204.1</v>
+        <v>2867.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>923.6</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>无（全程直连）</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
@@ -6537,14 +6421,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>O01→S014→O01</t>
+          <t>O01→S012→O01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1868.6</v>
+        <v>1923.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1373</v>
+        <v>2.7555</v>
       </c>
       <c r="I6" t="n">
         <v>25</v>
@@ -6553,16 +6437,16 @@
         <v>0.067</v>
       </c>
       <c r="K6" t="n">
-        <v>46.57</v>
+        <v>31.11</v>
       </c>
       <c r="L6" t="n">
-        <v>3461.4</v>
+        <v>3784.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>613.4</v>
+        <v>1152.2</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -6596,36 +6480,36 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>O01→S010→O01</t>
+          <t>O01→S011→O01</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1554.6</v>
+        <v>1126.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8211</v>
+        <v>1.0276</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>0.067</v>
+        <v>0.055</v>
       </c>
       <c r="K7" t="n">
-        <v>54.47</v>
+        <v>74.31</v>
       </c>
       <c r="L7" t="n">
-        <v>3010.4</v>
+        <v>2238.7</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>412.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>无（全程直连）</t>
         </is>
       </c>
     </row>
@@ -6655,26 +6539,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>O01→S006→S001→O01</t>
+          <t>O01→S001→O01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2257.3</v>
+        <v>1561.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5676</v>
+        <v>3.0047</v>
       </c>
       <c r="I8" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="J8" t="n">
-        <v>0.191</v>
+        <v>0.199</v>
       </c>
       <c r="K8" t="n">
-        <v>42.91</v>
+        <v>62.44</v>
       </c>
       <c r="L8" t="n">
-        <v>4327.7</v>
+        <v>3208.5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -6714,36 +6598,36 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O01→S002→O01</t>
+          <t>O01→S001→O01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2111</v>
+        <v>1627.4</v>
       </c>
       <c r="H9" t="n">
-        <v>6.1252</v>
+        <v>2.9263</v>
       </c>
       <c r="I9" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="J9" t="n">
-        <v>0.172</v>
+        <v>0.195</v>
       </c>
       <c r="K9" t="n">
-        <v>23.43</v>
+        <v>63.42</v>
       </c>
       <c r="L9" t="n">
-        <v>4603.3</v>
+        <v>3253.3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>941.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>无（全程直连）</t>
         </is>
       </c>
     </row>
@@ -6755,54 +6639,54 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A-B05</t>
+          <t>B-B03</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312.5</v>
+        <v>1126.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S010→O01</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2565</v>
+        <v>2681.3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2861</v>
+        <v>1.8211</v>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>0.055</v>
+        <v>0.067</v>
       </c>
       <c r="K10" t="n">
-        <v>71.42</v>
+        <v>54.47</v>
       </c>
       <c r="L10" t="n">
-        <v>3436.5</v>
+        <v>4137.1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>775.6</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>无（全程直连）</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6698,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6824,22 +6708,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A-B06</t>
+          <t>A-B05</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312.6</v>
+        <v>1312.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S006→O01</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2565.1</v>
+        <v>2625.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2861</v>
+        <v>1.355</v>
       </c>
       <c r="I11" t="n">
         <v>22</v>
@@ -6848,10 +6732,10 @@
         <v>0.055</v>
       </c>
       <c r="K11" t="n">
-        <v>71.42</v>
+        <v>69.89</v>
       </c>
       <c r="L11" t="n">
-        <v>3436.6</v>
+        <v>3516.8</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -6873,54 +6757,54 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B-B03</t>
+          <t>C-B03</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1554.6</v>
+        <v>1561.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>O01→S012→O01</t>
+          <t>O01→S006→S007→O01</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3478.5</v>
+        <v>3975.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7555</v>
+        <v>4.2979</v>
       </c>
       <c r="I12" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="J12" t="n">
-        <v>0.067</v>
+        <v>0.191</v>
       </c>
       <c r="K12" t="n">
-        <v>31.11</v>
+        <v>46.28</v>
       </c>
       <c r="L12" t="n">
-        <v>5339.2</v>
+        <v>5972.6</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>798.2</v>
+        <v>1087.6</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -6932,54 +6816,54 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>A-B06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1868.6</v>
+        <v>1612.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O01→S001→O01</t>
+          <t>O01→S011→S015→S003→O01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3019</v>
+        <v>4459.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.224</v>
+        <v>3.3583</v>
       </c>
       <c r="I13" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="K13" t="n">
-        <v>69.40000000000001</v>
+        <v>25.37</v>
       </c>
       <c r="L13" t="n">
-        <v>4216</v>
+        <v>5929.5</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1706.3</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>无（全程直连）</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -7001,44 +6885,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C-B03</t>
+          <t>C-B04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2111</v>
+        <v>1627.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O01→S007→S003→O01</t>
+          <t>O01→S002→O01</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4804.4</v>
+        <v>3804.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.9452</v>
+        <v>6.301</v>
       </c>
       <c r="I14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J14" t="n">
-        <v>0.167</v>
+        <v>0.184</v>
       </c>
       <c r="K14" t="n">
-        <v>25.68</v>
+        <v>21.24</v>
       </c>
       <c r="L14" t="n">
-        <v>7247.9</v>
+        <v>6344.4</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1287.5</v>
+        <v>979.2</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
@@ -7050,54 +6934,54 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A-B02</t>
+          <t>B-B04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2178.8</v>
+        <v>1923.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>O01→S011→O01</t>
+          <t>O01→S014→O01</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3399.4</v>
+        <v>3792.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1937</v>
+        <v>2.1373</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>0.055</v>
+        <v>0.067</v>
       </c>
       <c r="K15" t="n">
-        <v>73.47</v>
+        <v>46.57</v>
       </c>
       <c r="L15" t="n">
-        <v>4244.2</v>
+        <v>5385.3</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>721.3</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>无（全程直连）</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
@@ -7109,50 +6993,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C-B04</t>
+          <t>A-B03</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2257.3</v>
+        <v>2191</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>O01→S001→S005→O01</t>
+          <t>O01→S015→O01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4500.8</v>
+        <v>4161.3</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8182</v>
+        <v>2.5617</v>
       </c>
       <c r="I16" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>0.206</v>
+        <v>0.055</v>
       </c>
       <c r="K16" t="n">
-        <v>39.77</v>
+        <v>43.07</v>
       </c>
       <c r="L16" t="n">
-        <v>6639</v>
+        <v>5401.3</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>634.8</v>
+        <v>1130.6</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -7168,50 +7052,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A-B04</t>
+          <t>B-B02</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2466.8</v>
+        <v>2681.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>O01→S011→S005→O01</t>
+          <t>O01→S008→O01</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4475</v>
+        <v>4587.2</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2522</v>
+        <v>2.7735</v>
       </c>
       <c r="I17" t="n">
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>0.051</v>
+        <v>0.062</v>
       </c>
       <c r="K17" t="n">
-        <v>49.95</v>
+        <v>30.66</v>
       </c>
       <c r="L17" t="n">
-        <v>5625.6</v>
+        <v>6455.7</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>496.2</v>
+        <v>1166.3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -7227,50 +7111,50 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B-B02</t>
+          <t>A-B01</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3019</v>
+        <v>2697.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>O01→S008→O01</t>
+          <t>O01→S005→O01</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4924.9</v>
+        <v>4393</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7735</v>
+        <v>2.2015</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>0.062</v>
+        <v>0.055</v>
       </c>
       <c r="K18" t="n">
-        <v>30.66</v>
+        <v>51.08</v>
       </c>
       <c r="L18" t="n">
-        <v>6793.4</v>
+        <v>5528.9</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>778.4</v>
+        <v>936.3</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -7286,7 +7170,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7300,7 +7184,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3478.5</v>
+        <v>3792.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7308,7 +7192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5444.4</v>
+        <v>5758.4</v>
       </c>
       <c r="H19" t="n">
         <v>2.9861</v>
@@ -7323,13 +7207,13 @@
         <v>25.35</v>
       </c>
       <c r="L19" t="n">
-        <v>7405</v>
+        <v>7719</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>808.4</v>
+        <v>1196.3</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -7345,7 +7229,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7359,40 +7243,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4500.8</v>
+        <v>3804.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>O01→S007→S003→O01</t>
+          <t>O01→S005→S004→O01</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7128.2</v>
+        <v>6522.4</v>
       </c>
       <c r="H20" t="n">
-        <v>5.6737</v>
+        <v>6.3448</v>
       </c>
       <c r="I20" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J20" t="n">
-        <v>0.173</v>
+        <v>0.203</v>
       </c>
       <c r="K20" t="n">
-        <v>29.08</v>
+        <v>20.69</v>
       </c>
       <c r="L20" t="n">
-        <v>9498.1</v>
+        <v>9074.1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1251.5</v>
+        <v>1345.2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R02,Q3-R03</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7288,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7418,40 +7302,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4804.4</v>
+        <v>3975.3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>O01→S004→O01</t>
+          <t>O01→S003→O01</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>7109.6</v>
+        <v>6477.2</v>
       </c>
       <c r="H21" t="n">
-        <v>6.1769</v>
+        <v>6.3228</v>
       </c>
       <c r="I21" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J21" t="n">
-        <v>0.156</v>
+        <v>0.184</v>
       </c>
       <c r="K21" t="n">
-        <v>22.79</v>
+        <v>20.96</v>
       </c>
       <c r="L21" t="n">
-        <v>9615.9</v>
+        <v>9023</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>832.3</v>
+        <v>1078.7</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Q3-R02,Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7347,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7473,103 +7357,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B-B04</t>
+          <t>B-B03</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4924.9</v>
+        <v>4587.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>O01→S015→O01</t>
+          <t>O01→S004→O01</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>6754.5</v>
+        <v>6513.1</v>
       </c>
       <c r="H22" t="n">
-        <v>2.311</v>
+        <v>3.047</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>0.067</v>
+        <v>0.054</v>
       </c>
       <c r="K22" t="n">
-        <v>42.22</v>
+        <v>23.83</v>
       </c>
       <c r="L22" t="n">
-        <v>8422.6</v>
+        <v>8500.1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>589.7</v>
+        <v>620.3</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q3-T22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>B-B03</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>5444.4</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>O01→S009→O01</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>7005.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.1025</v>
-      </c>
-      <c r="I23" t="n">
-        <v>25</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="K23" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="L23" t="n">
-        <v>8582.9</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>521.9</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
+          <t>Q3-R02,Q3-R03</t>
         </is>
       </c>
     </row>
@@ -7637,7 +7462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7646,7 +7471,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1944.8</v>
+        <v>1314.9</v>
       </c>
       <c r="E2" t="n">
         <v>7200</v>
@@ -7669,7 +7494,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Q3-T10</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7678,7 +7503,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2222</v>
+        <v>1248.9</v>
       </c>
       <c r="E3" t="n">
         <v>7200</v>
@@ -7701,7 +7526,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q3-T09</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7710,7 +7535,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2221.8</v>
+        <v>1248.9</v>
       </c>
       <c r="E4" t="n">
         <v>7200</v>
@@ -7733,7 +7558,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7742,7 +7567,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1944.8</v>
+        <v>1314.9</v>
       </c>
       <c r="E5" t="n">
         <v>10800</v>
@@ -7765,7 +7590,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7774,7 +7599,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3362.2</v>
+        <v>1248.9</v>
       </c>
       <c r="E6" t="n">
         <v>10800</v>
@@ -7797,7 +7622,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q3-T02</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7806,7 +7631,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>969.4</v>
+        <v>1314.9</v>
       </c>
       <c r="E7" t="n">
         <v>3600</v>
@@ -7831,7 +7656,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q3-T02</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7840,7 +7665,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>969.4</v>
+        <v>1314.9</v>
       </c>
       <c r="E8" t="n">
         <v>3600</v>
@@ -7865,7 +7690,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q3-T10</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7874,7 +7699,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2222</v>
+        <v>1314.9</v>
       </c>
       <c r="E9" t="n">
         <v>3600</v>
@@ -7899,7 +7724,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7908,7 +7733,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1944.8</v>
+        <v>1314.9</v>
       </c>
       <c r="E10" t="n">
         <v>3600</v>
@@ -7931,7 +7756,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7940,7 +7765,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3362.2</v>
+        <v>1314.9</v>
       </c>
       <c r="E11" t="n">
         <v>3600</v>
@@ -7963,7 +7788,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q3-T09</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7972,7 +7797,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2221.8</v>
+        <v>1248.9</v>
       </c>
       <c r="E12" t="n">
         <v>3600</v>
@@ -7995,7 +7820,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8004,7 +7829,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2726.9</v>
+        <v>1248.9</v>
       </c>
       <c r="E13" t="n">
         <v>3600</v>
@@ -8027,7 +7852,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Q3-T02</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8036,7 +7861,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>969.4</v>
+        <v>1248.9</v>
       </c>
       <c r="E14" t="n">
         <v>3600</v>
@@ -8059,7 +7884,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8068,7 +7893,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3362.2</v>
+        <v>1248.9</v>
       </c>
       <c r="E15" t="n">
         <v>3600</v>
@@ -8091,7 +7916,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q3-T12</t>
+          <t>Q3-T08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8100,7 +7925,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2726.9</v>
+        <v>1314.9</v>
       </c>
       <c r="E16" t="n">
         <v>3600</v>
@@ -8123,7 +7948,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8132,7 +7957,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E17" t="n">
         <v>7200</v>
@@ -8155,7 +7980,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8164,7 +7989,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E18" t="n">
         <v>7200</v>
@@ -8187,7 +8012,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8196,7 +8021,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E19" t="n">
         <v>10800</v>
@@ -8219,7 +8044,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8228,7 +8053,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1315.8</v>
+        <v>3182.4</v>
       </c>
       <c r="E20" t="n">
         <v>3600</v>
@@ -8253,7 +8078,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8262,7 +8087,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E21" t="n">
         <v>3600</v>
@@ -8287,7 +8112,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8296,7 +8121,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1315.8</v>
+        <v>1527.9</v>
       </c>
       <c r="E22" t="n">
         <v>3600</v>
@@ -8319,7 +8144,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8328,7 +8153,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E23" t="n">
         <v>3600</v>
@@ -8351,7 +8176,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q3-T08</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8360,7 +8185,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1488.9</v>
+        <v>3182.4</v>
       </c>
       <c r="E24" t="n">
         <v>3600</v>
@@ -8383,7 +8208,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q3-T19</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8392,7 +8217,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6337.7</v>
+        <v>5686.7</v>
       </c>
       <c r="E25" t="n">
         <v>10800</v>
@@ -8415,7 +8240,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q3-T19</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8424,7 +8249,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6337.7</v>
+        <v>5686.7</v>
       </c>
       <c r="E26" t="n">
         <v>10800</v>
@@ -8447,7 +8272,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8456,7 +8281,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4014</v>
+        <v>5686.7</v>
       </c>
       <c r="E27" t="n">
         <v>14400</v>
@@ -8479,7 +8304,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8488,7 +8313,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4014</v>
+        <v>5686.7</v>
       </c>
       <c r="E28" t="n">
         <v>7200</v>
@@ -8513,7 +8338,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8522,7 +8347,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4014</v>
+        <v>5686.7</v>
       </c>
       <c r="E29" t="n">
         <v>7200</v>
@@ -8547,7 +8372,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q3-T19</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8556,7 +8381,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6337.7</v>
+        <v>5686.7</v>
       </c>
       <c r="E30" t="n">
         <v>7200</v>
@@ -8579,7 +8404,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Q3-T19</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8588,7 +8413,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6337.7</v>
+        <v>3606.1</v>
       </c>
       <c r="E31" t="n">
         <v>7200</v>
@@ -8611,7 +8436,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8620,7 +8445,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4014</v>
+        <v>5686.7</v>
       </c>
       <c r="E32" t="n">
         <v>7200</v>
@@ -8643,7 +8468,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8652,7 +8477,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6390</v>
+        <v>5802.8</v>
       </c>
       <c r="E33" t="n">
         <v>10800</v>
@@ -8675,7 +8500,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8684,7 +8509,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6390</v>
+        <v>5802.8</v>
       </c>
       <c r="E34" t="n">
         <v>14400</v>
@@ -8707,7 +8532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8716,7 +8541,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6390</v>
+        <v>5802.8</v>
       </c>
       <c r="E35" t="n">
         <v>7200</v>
@@ -8741,7 +8566,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8750,7 +8575,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6390</v>
+        <v>5802.8</v>
       </c>
       <c r="E36" t="n">
         <v>7200</v>
@@ -8775,7 +8600,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8784,7 +8609,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6390</v>
+        <v>5831.8</v>
       </c>
       <c r="E37" t="n">
         <v>7200</v>
@@ -8807,7 +8632,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Q3-T20</t>
+          <t>Q3-T21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8816,7 +8641,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6390</v>
+        <v>5831.8</v>
       </c>
       <c r="E38" t="n">
         <v>7200</v>
@@ -8839,7 +8664,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8848,7 +8673,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3995.4</v>
+        <v>3827.8</v>
       </c>
       <c r="E39" t="n">
         <v>14400</v>
@@ -8871,7 +8696,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8880,7 +8705,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3995.4</v>
+        <v>5167.3</v>
       </c>
       <c r="E40" t="n">
         <v>18000</v>
@@ -8903,7 +8728,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8912,7 +8737,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3909.9</v>
+        <v>5167.3</v>
       </c>
       <c r="E41" t="n">
         <v>10800</v>
@@ -8937,7 +8762,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8946,7 +8771,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3909.9</v>
+        <v>5167.3</v>
       </c>
       <c r="E42" t="n">
         <v>10800</v>
@@ -8971,7 +8796,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8980,7 +8805,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3995.4</v>
+        <v>5167.3</v>
       </c>
       <c r="E43" t="n">
         <v>10800</v>
@@ -9003,7 +8828,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9012,7 +8837,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3995.4</v>
+        <v>3827.8</v>
       </c>
       <c r="E44" t="n">
         <v>10800</v>
@@ -9035,7 +8860,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9044,7 +8869,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>935.1</v>
+        <v>2247.8</v>
       </c>
       <c r="E45" t="n">
         <v>7200</v>
@@ -9067,7 +8892,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -9076,7 +8901,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1167.1</v>
+        <v>2656.6</v>
       </c>
       <c r="E46" t="n">
         <v>10800</v>
@@ -9099,7 +8924,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9108,7 +8933,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1167.1</v>
+        <v>935.1</v>
       </c>
       <c r="E47" t="n">
         <v>3600</v>
@@ -9133,7 +8958,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9142,7 +8967,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1167.1</v>
+        <v>935.1</v>
       </c>
       <c r="E48" t="n">
         <v>3600</v>
@@ -9167,7 +8992,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q3-T04</t>
+          <t>Q3-T10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9176,7 +9001,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>935.1</v>
+        <v>2247.8</v>
       </c>
       <c r="E49" t="n">
         <v>3600</v>
@@ -9199,7 +9024,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q3-T07</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9208,7 +9033,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1167.1</v>
+        <v>2656.6</v>
       </c>
       <c r="E50" t="n">
         <v>3600</v>
@@ -9231,7 +9056,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Q3-T19</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9240,7 +9065,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5770.5</v>
+        <v>3415.5</v>
       </c>
       <c r="E51" t="n">
         <v>7200</v>
@@ -9263,7 +9088,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Q3-T19</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -9272,7 +9097,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5770.5</v>
+        <v>3415.5</v>
       </c>
       <c r="E52" t="n">
         <v>10800</v>
@@ -9295,7 +9120,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -9304,7 +9129,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3446.8</v>
+        <v>3415.5</v>
       </c>
       <c r="E53" t="n">
         <v>3600</v>
@@ -9329,7 +9154,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9338,7 +9163,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3446.8</v>
+        <v>3415.5</v>
       </c>
       <c r="E54" t="n">
         <v>3600</v>
@@ -9363,7 +9188,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9372,7 +9197,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3446.8</v>
+        <v>3415.5</v>
       </c>
       <c r="E55" t="n">
         <v>3600</v>
@@ -9404,7 +9229,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4771.7</v>
+        <v>5085.7</v>
       </c>
       <c r="E56" t="n">
         <v>10800</v>
@@ -9427,7 +9252,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Q3-T17</t>
+          <t>Q3-T16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9436,7 +9261,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4252.1</v>
+        <v>3914.5</v>
       </c>
       <c r="E57" t="n">
         <v>14400</v>
@@ -9468,7 +9293,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4771.7</v>
+        <v>5085.7</v>
       </c>
       <c r="E58" t="n">
         <v>7200</v>
@@ -9502,7 +9327,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4771.7</v>
+        <v>5085.7</v>
       </c>
       <c r="E59" t="n">
         <v>7200</v>
@@ -9527,7 +9352,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q3-T17</t>
+          <t>Q3-T16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9536,7 +9361,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4252.1</v>
+        <v>3914.5</v>
       </c>
       <c r="E60" t="n">
         <v>7200</v>
@@ -9559,7 +9384,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Q3-T22</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9568,7 +9393,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6536.4</v>
+        <v>1127.4</v>
       </c>
       <c r="E61" t="n">
         <v>14400</v>
@@ -9591,7 +9416,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q3-T22</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9600,7 +9425,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6536.4</v>
+        <v>1127.4</v>
       </c>
       <c r="E62" t="n">
         <v>10800</v>
@@ -9625,7 +9450,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q3-T22</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9634,7 +9459,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6536.4</v>
+        <v>1127.4</v>
       </c>
       <c r="E63" t="n">
         <v>10800</v>
@@ -9659,7 +9484,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9668,7 +9493,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1084.8</v>
+        <v>2211.5</v>
       </c>
       <c r="E64" t="n">
         <v>7200</v>
@@ -9691,7 +9516,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9700,7 +9525,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1084.8</v>
+        <v>2211.5</v>
       </c>
       <c r="E65" t="n">
         <v>3600</v>
@@ -9725,7 +9550,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q3-T06</t>
+          <t>Q3-T09</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9734,7 +9559,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1084.8</v>
+        <v>2211.5</v>
       </c>
       <c r="E66" t="n">
         <v>3600</v>
@@ -9759,7 +9584,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9768,7 +9593,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3071.3</v>
+        <v>845.5</v>
       </c>
       <c r="E67" t="n">
         <v>14400</v>
@@ -9791,7 +9616,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q3-T16</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9800,7 +9625,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3359.3</v>
+        <v>2504.6</v>
       </c>
       <c r="E68" t="n">
         <v>10800</v>
@@ -9825,7 +9650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q3-T14</t>
+          <t>Q3-T06</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9834,7 +9659,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3071.3</v>
+        <v>845.5</v>
       </c>
       <c r="E69" t="n">
         <v>10800</v>
@@ -9859,7 +9684,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q3-T11</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9868,7 +9693,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
       <c r="E70" t="n">
         <v>7200</v>
@@ -9891,7 +9716,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Q3-T11</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9900,7 +9725,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
       <c r="E71" t="n">
         <v>7200</v>
@@ -9925,7 +9750,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q3-T11</t>
+          <t>Q3-T05</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9934,7 +9759,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2826.5</v>
+        <v>1271.9</v>
       </c>
       <c r="E72" t="n">
         <v>3600</v>
@@ -9959,7 +9784,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9991,7 +9816,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10000,7 +9825,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1938.3</v>
+        <v>2150.4</v>
       </c>
       <c r="E74" t="n">
         <v>3600</v>
@@ -10025,7 +9850,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10059,7 +9884,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10068,7 +9893,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1241.9</v>
+        <v>3165.8</v>
       </c>
       <c r="E76" t="n">
         <v>7200</v>
@@ -10091,7 +9916,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10100,7 +9925,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1241.9</v>
+        <v>3165.8</v>
       </c>
       <c r="E77" t="n">
         <v>7200</v>
@@ -10125,7 +9950,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Q3-T05</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10134,7 +9959,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1241.9</v>
+        <v>3165.8</v>
       </c>
       <c r="E78" t="n">
         <v>3600</v>
@@ -10159,7 +9984,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Q3-T21</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10168,7 +9993,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6143.1</v>
+        <v>3449.6</v>
       </c>
       <c r="E79" t="n">
         <v>14400</v>
@@ -10191,7 +10016,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q3-T21</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -10200,7 +10025,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6143.1</v>
+        <v>3144</v>
       </c>
       <c r="E80" t="n">
         <v>7200</v>
@@ -10225,7 +10050,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Q3-T21</t>
+          <t>Q3-T15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -10234,7 +10059,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6143.1</v>
+        <v>3449.6</v>
       </c>
       <c r="E81" t="n">
         <v>10800</v>
@@ -10312,11 +10137,11 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>4475</v>
+        <v>4459.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Q3-T01,Q3-T16</t>
+          <t>Q3-T01,Q3-T12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -10333,14 +10158,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2565</v>
+        <v>2678.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Q3-T02,Q3-T09</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -10357,14 +10182,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2832.7</v>
+        <v>4321</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Q3-T03,Q3-T14</t>
+          <t>Q3-T03,Q3-T10,Q3-T17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -10384,11 +10209,11 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2565.1</v>
+        <v>3661.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Q3-T04,Q3-T10</t>
+          <t>Q3-T04,Q3-T15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -10405,14 +10230,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6754.5</v>
+        <v>5758.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Q3-T05,Q3-T12,Q3-T17,Q3-T21</t>
+          <t>Q3-T05,Q3-T14,Q3-T18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -10432,11 +10257,11 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>7005.2</v>
+        <v>6513</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Q3-T06,Q3-T11,Q3-T18,Q3-T22</t>
+          <t>Q3-T06,Q3-T09,Q3-T16,Q3-T21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -10456,11 +10281,11 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>7128.2</v>
+        <v>6477.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Q3-T07,Q3-T15,Q3-T19</t>
+          <t>Q3-T07,Q3-T11,Q3-T20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -10480,11 +10305,11 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>7109.6</v>
+        <v>6522.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Q3-T08,Q3-T13,Q3-T20</t>
+          <t>Q3-T08,Q3-T13,Q3-T19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -10501,18 +10326,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2466.8</v>
+        <v>3307.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Q3-T01</t>
+          <t>Q3-T01,Q3-T17</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1476.4</v>
+        <v>2221.1</v>
       </c>
     </row>
     <row r="11">
@@ -10527,18 +10352,18 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2533.1</v>
+        <v>2678.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Q3-T02,Q3-T14</t>
+          <t>Q3-T02</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1711.2</v>
+        <v>1481.6</v>
       </c>
     </row>
     <row r="12">
@@ -10553,18 +10378,18 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1612.1</v>
+        <v>3282.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Q3-T03</t>
+          <t>Q3-T03,Q3-T15</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1085.1</v>
+        <v>2118.4</v>
       </c>
     </row>
     <row r="13">
@@ -10579,18 +10404,18 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3320.8</v>
+        <v>1691.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Q3-T04,Q3-T16</t>
+          <t>Q3-T04</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2042.1</v>
+        <v>1175.5</v>
       </c>
     </row>
     <row r="14">
@@ -10608,15 +10433,15 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1252.5</v>
+        <v>1312.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Q3-T09</t>
+          <t>Q3-T10</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>871.5</v>
+        <v>891.4</v>
       </c>
     </row>
     <row r="15">
@@ -10634,15 +10459,15 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1252.5</v>
+        <v>2847.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Q3-T10</t>
+          <t>Q3-T12</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>871.5</v>
+        <v>1470.2</v>
       </c>
     </row>
     <row r="16">
@@ -10660,7 +10485,7 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3834.5</v>
+        <v>3889.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -10668,7 +10493,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3553.4</v>
+        <v>3821.3</v>
       </c>
     </row>
     <row r="17">
@@ -10686,15 +10511,15 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3460.5</v>
+        <v>3032.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Q3-T06,Q3-T17</t>
+          <t>Q3-T06,Q3-T16</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3324.3</v>
+        <v>2980.5</v>
       </c>
     </row>
     <row r="18">
@@ -10712,15 +10537,15 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3484.7</v>
+        <v>3480.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Q3-T11,Q3-T22</t>
+          <t>Q3-T09,Q3-T21</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3438.5</v>
+        <v>3442.8</v>
       </c>
     </row>
     <row r="19">
@@ -10735,18 +10560,18 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2980</v>
+        <v>1868.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Q3-T12,Q3-T21</t>
+          <t>Q3-T14</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2865.2</v>
+        <v>1592.8</v>
       </c>
     </row>
     <row r="20">
@@ -10764,7 +10589,7 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>4884.7</v>
+        <v>4279.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -10772,7 +10597,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4440.3</v>
+        <v>4198.8</v>
       </c>
     </row>
     <row r="21">
@@ -10790,7 +10615,7 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>4416.2</v>
+        <v>4129.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -10798,7 +10623,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4998.5</v>
+        <v>4171.6</v>
       </c>
     </row>
     <row r="22">
@@ -10816,15 +10641,15 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2693.4</v>
+        <v>2413.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Q3-T13</t>
+          <t>Q3-T11</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2443.5</v>
+        <v>1997.3</v>
       </c>
     </row>
     <row r="23">
@@ -10842,15 +10667,15 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2243.4</v>
+        <v>2177</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Q3-T15</t>
+          <t>Q3-T13</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2138.3</v>
+        <v>2539.8</v>
       </c>
     </row>
     <row r="24">
@@ -10868,7 +10693,7 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>5442.9</v>
+        <v>5711.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -10892,7 +10717,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4710.6</v>
+        <v>4321.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -10913,18 +10738,18 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5442.9</v>
+        <v>3910.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Q3-R01,Q3-R03</t>
+          <t>Q3-R01</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1604.1</v>
+        <v>947.5</v>
       </c>
     </row>
     <row r="27">
@@ -10942,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>4710.6</v>
+        <v>4321.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -10950,7 +10775,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1045.6</v>
+        <v>997.4</v>
       </c>
     </row>
     <row r="28">
@@ -10965,14 +10790,18 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+        <v>1800.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>688.8</v>
       </c>
     </row>
     <row r="29">
@@ -11098,7 +10927,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>最低返航SOC 22.79%</t>
+          <t>最低返航SOC 20.69%</t>
         </is>
       </c>
     </row>
@@ -11143,7 +10972,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>最低返航SOC 58.03%</t>
+          <t>最低返航SOC 61.74%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +10987,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>使用中继 2 架，能源组件 2 组</t>
+          <t>使用中继 2 架，能源组件 3 组</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11020,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>逐秒复核：运输机飞行与投送全程通信不中断</t>
+          <t>0.1 s 精细复核：运输机飞行与投送全程通信不中断</t>
         </is>
       </c>
       <c r="B10" t="b">
@@ -11199,7 +11028,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>飞行+投送共 31435 s：直连 19825 s，中继 11611 s，中断 0 s</t>
+          <t>飞行+投送共 31691.7 s：直连 14182.0 s，中继 17509.8 s，中断 0.00 s；保障方式切换 34 次，切换处新旧方式同时可用的最短重叠 1.352 s</t>
         </is>
       </c>
     </row>
@@ -11292,19 +11121,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>66.85599999999999</v>
+        <v>64.459</v>
       </c>
       <c r="E2" t="n">
-        <v>4.17</v>
+        <v>3.737</v>
       </c>
       <c r="F2" t="n">
-        <v>71.026</v>
+        <v>68.196</v>
       </c>
       <c r="G2" t="n">
-        <v>7392.2</v>
+        <v>7333.4</v>
       </c>
       <c r="H2" t="n">
-        <v>7653.3</v>
+        <v>7586.5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -11316,7 +11145,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>682.24</v>
+        <v>665.87</v>
       </c>
     </row>
     <row r="3">
@@ -11329,22 +11158,22 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>66.887</v>
+        <v>65.134</v>
       </c>
       <c r="E3" t="n">
-        <v>3.397</v>
+        <v>3.284</v>
       </c>
       <c r="F3" t="n">
-        <v>70.285</v>
+        <v>68.41800000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>7392.2</v>
+        <v>6543.2</v>
       </c>
       <c r="H3" t="n">
-        <v>7421.2</v>
+        <v>6572.9</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -11356,7 +11185,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>673.8</v>
+        <v>633.1900000000001</v>
       </c>
     </row>
     <row r="4">
@@ -11366,25 +11195,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>65.56699999999999</v>
+        <v>64.51600000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.824</v>
+        <v>2.989</v>
       </c>
       <c r="F4" t="n">
-        <v>68.39100000000001</v>
+        <v>67.505</v>
       </c>
       <c r="G4" t="n">
-        <v>7194.2</v>
+        <v>6543.2</v>
       </c>
       <c r="H4" t="n">
-        <v>7194.2</v>
+        <v>6546.6</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -11396,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>656.76</v>
+        <v>627.75</v>
       </c>
     </row>
     <row r="5">
@@ -11412,19 +11241,19 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>66.208</v>
+        <v>68.812</v>
       </c>
       <c r="E5" t="n">
-        <v>2.859</v>
+        <v>2.849</v>
       </c>
       <c r="F5" t="n">
-        <v>69.06699999999999</v>
+        <v>71.66200000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>7128.2</v>
+        <v>6411.2</v>
       </c>
       <c r="H5" t="n">
-        <v>7128.2</v>
+        <v>6411.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -11436,7 +11265,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>660.9400000000001</v>
+        <v>650.02</v>
       </c>
     </row>
     <row r="6">
@@ -11446,25 +11275,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>65.464</v>
+        <v>63.607</v>
       </c>
       <c r="E6" t="n">
-        <v>2.821</v>
+        <v>3.216</v>
       </c>
       <c r="F6" t="n">
-        <v>68.285</v>
+        <v>66.82299999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>7128.2</v>
+        <v>7624.2</v>
       </c>
       <c r="H6" t="n">
-        <v>7142.3</v>
+        <v>7692.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11476,7 +11305,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>654.5</v>
+        <v>662.52</v>
       </c>
     </row>
     <row r="7">
@@ -11486,25 +11315,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>65.56699999999999</v>
+        <v>64.51600000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.824</v>
+        <v>2.989</v>
       </c>
       <c r="F7" t="n">
-        <v>68.39100000000001</v>
+        <v>67.505</v>
       </c>
       <c r="G7" t="n">
-        <v>7194.2</v>
+        <v>6543.2</v>
       </c>
       <c r="H7" t="n">
-        <v>7194.2</v>
+        <v>6546.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11516,7 +11345,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>656.76</v>
+        <v>627.75</v>
       </c>
     </row>
     <row r="8">
@@ -11526,25 +11355,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>65.464</v>
+        <v>64.29300000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.83</v>
+        <v>2.791</v>
       </c>
       <c r="F8" t="n">
-        <v>68.294</v>
+        <v>67.084</v>
       </c>
       <c r="G8" t="n">
-        <v>7128.2</v>
+        <v>6522.4</v>
       </c>
       <c r="H8" t="n">
-        <v>7136.8</v>
+        <v>6560</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11556,7 +11385,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>654.36</v>
+        <v>626.08</v>
       </c>
     </row>
   </sheetData>
@@ -11949,28 +11778,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>109.279108</v>
+        <v>109.278483</v>
       </c>
       <c r="C2" t="n">
-        <v>23.01896</v>
+        <v>23.02146</v>
       </c>
       <c r="D2" t="n">
-        <v>696.8</v>
+        <v>663.2</v>
       </c>
       <c r="E2" t="n">
-        <v>396.8</v>
+        <v>363.2</v>
       </c>
       <c r="F2" t="n">
-        <v>5074</v>
+        <v>5083</v>
       </c>
       <c r="G2" t="n">
-        <v>480.5</v>
+        <v>472.8</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2667</v>
+        <v>0.2641</v>
       </c>
       <c r="I2" t="n">
-        <v>7475</v>
+        <v>7484</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -11990,37 +11819,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>109.228858</v>
+        <v>109.201483</v>
       </c>
       <c r="C3" t="n">
-        <v>23.06271</v>
+        <v>23.032835</v>
       </c>
       <c r="D3" t="n">
-        <v>528.3</v>
+        <v>672.5</v>
       </c>
       <c r="E3" t="n">
-        <v>228.3</v>
+        <v>372.5</v>
       </c>
       <c r="F3" t="n">
-        <v>6030</v>
+        <v>4044</v>
       </c>
       <c r="G3" t="n">
-        <v>502.2</v>
+        <v>405.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2925</v>
+        <v>0.2207</v>
       </c>
       <c r="I3" t="n">
-        <v>7391</v>
+        <v>7626</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S013</t>
+          <t>S003,S005,S007,S008,S009,S015</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
@@ -12031,35 +11860,39 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>109.223858</v>
+        <v>109.247608</v>
       </c>
       <c r="C4" t="n">
-        <v>23.02021</v>
+        <v>23.056585</v>
       </c>
       <c r="D4" t="n">
-        <v>458.7</v>
+        <v>586.5</v>
       </c>
       <c r="E4" t="n">
-        <v>158.7</v>
+        <v>286.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1485</v>
+        <v>5614</v>
       </c>
       <c r="G4" t="n">
-        <v>181.8</v>
+        <v>489</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0927</v>
+        <v>0.2799</v>
       </c>
       <c r="I4" t="n">
-        <v>8045</v>
+        <v>7432</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>S009,S013</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>S002,S004,S005,S009,S013</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12068,39 +11901,35 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>109.201358</v>
+        <v>109.241358</v>
       </c>
       <c r="C5" t="n">
-        <v>23.03296</v>
+        <v>23.02771</v>
       </c>
       <c r="D5" t="n">
-        <v>675.4</v>
+        <v>548.3</v>
       </c>
       <c r="E5" t="n">
-        <v>375.4</v>
+        <v>248.3</v>
       </c>
       <c r="F5" t="n">
-        <v>4063</v>
+        <v>2390</v>
       </c>
       <c r="G5" t="n">
-        <v>407.8</v>
+        <v>264.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2217</v>
+        <v>0.1392</v>
       </c>
       <c r="I5" t="n">
-        <v>7622</v>
+        <v>7893</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>S003,S005,S007,S008,S009,S015</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>S005,S009,S013</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
